--- a/web/public/forms/jakeop-ilbo.xlsx
+++ b/web/public/forms/jakeop-ilbo.xlsx
@@ -193,7 +193,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -202,7 +202,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -217,37 +217,37 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -262,6 +262,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2125,6 +2130,26 @@
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A65:L65"/>
   </mergeCells>
+  <conditionalFormatting sqref="D12:D23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(D12),MOD(D12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F23">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(F12),MOD(F12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G23">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(G12),MOD(G12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H23">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(H12),MOD(H12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3877,6 +3902,26 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="B51:F51"/>
   </mergeCells>
+  <conditionalFormatting sqref="D12:D23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(D12),MOD(D12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F23">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(F12),MOD(F12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G23">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(G12),MOD(G12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H23">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(H12),MOD(H12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5638,6 +5683,26 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="B51:F51"/>
   </mergeCells>
+  <conditionalFormatting sqref="D12:D23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(D12),MOD(D12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F23">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(F12),MOD(F12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G23">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>AND(ISNUMBER(G12),MOD(G12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H23">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>AND(ISNUMBER(H12),MOD(H12,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/public/forms/jakeop-ilbo.xlsx
+++ b/web/public/forms/jakeop-ilbo.xlsx
@@ -650,7 +650,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="33" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="33" t="inlineStr">

--- a/web/public/forms/jakeop-ilbo.xlsx
+++ b/web/public/forms/jakeop-ilbo.xlsx
@@ -638,7 +638,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
